--- a/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:52</t>
+          <t>2026-10-06 01:24:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:53</t>
+          <t>2026-10-06 01:24:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:54</t>
+          <t>2026-10-06 01:24:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:56</t>
+          <t>2026-10-06 01:25:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:56</t>
+          <t>2026-10-06 01:25:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:56</t>
+          <t>2026-10-06 01:25:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:56</t>
+          <t>2026-10-06 01:25:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:56</t>
+          <t>2026-10-06 01:25:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:57</t>
+          <t>2026-10-06 02:28:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:58</t>
+          <t>2026-10-06 02:28:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:59</t>
+          <t>2026-10-06 02:28:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:25:01</t>
+          <t>2026-10-06 02:28:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.86%830,000</t>
+          <t>8.98%830,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.86%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1325</v>
+        <v>1310</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.02%1,097,000</t>
+          <t>6.01%1,097,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.02%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5165</v>
+        <v>3685</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.76%269,000</t>
+          <t>5.78%375,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.76%</t>
+          <t>5.78%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>269000</v>
+        <v>375000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3585</v>
+        <v>5995</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.57%375,000</t>
+          <t>5.64%225,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.57%</t>
+          <t>5.64%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>375000</v>
+        <v>225000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5700</v>
+        <v>4920</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.32%225,000</t>
+          <t>5.54%269,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>225000</v>
+        <v>269000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8600</v>
+        <v>8375</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.10%143,000</t>
+          <t>5.01%143,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1780</v>
+        <v>2290</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.98%539,000</t>
+          <t>4.00%417,644</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>539000</v>
+        <v>417644</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2150</v>
+        <v>1755</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.72%417,644</t>
+          <t>3.96%539,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>417644</v>
+        <v>539000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.46%116,000</t>
+          <t>3.44%116,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.99%483,000</t>
+          <t>3.04%483,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.93%952,000</t>
+          <t>2.96%952,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2485</v>
+        <v>2050</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.86%278,000</t>
+          <t>2.77%323,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>278000</v>
+        <v>323000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13355</v>
+        <v>13100</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.77%50,000</t>
+          <t>2.74%50,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2005</v>
+        <v>2325</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.68%323,000</t>
+          <t>2.70%278,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>323000</v>
+        <v>278000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:26</t>
+          <t>2026-10-06 19:17:34</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.61%114,000</t>
+          <t>2.70%114,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>-0.16%625</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.32%895,000</t>
+          <t>2.34%895,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+5.63%1595</t>
+          <t>+0.31%1600</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.14%324,000</t>
+          <t>2.17%324,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19520</v>
+        <v>18985</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.77%21,900</t>
+          <t>1.74%21,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+9.96%1490</t>
+          <t>+3.02%1535</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1490</v>
+        <v>1535</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.57%255,000</t>
+          <t>1.64%255,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6730</v>
+        <v>6855</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.45%52,000</t>
+          <t>1.49%52,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+5.86%298</t>
+          <t>+0.34%299</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.43%1,160,000</t>
+          <t>1.45%1,160,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+2.56%3000</t>
+          <t>-2.67%2920</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3000</v>
+        <v>2920</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.40%113,000</t>
+          <t>1.38%113,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.14%3105</t>
+          <t>-1.61%3055</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3105</v>
+        <v>3055</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.22%95,000</t>
+          <t>1.21%95,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+6.06%2450</t>
+          <t>-1.43%2415</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+6.06%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2450</v>
+        <v>2415</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.14%112,000</t>
+          <t>1.13%112,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.46%1040</t>
+          <t>-0.96%1030</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.01%105,000</t>
+          <t>1.03%105,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.67%576</t>
+          <t>-0.35%574</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.76%530</t>
+          <t>+5.21%1715</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+5.21%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>530</v>
+        <v>1715</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.94%426,000</t>
+          <t>0.97%135,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>426000</v>
+        <v>135000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:27</t>
+          <t>2026-10-06 19:17:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+9.76%1630</t>
+          <t>-0.94%525</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+9.76%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1630</v>
+        <v>525</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.91%135,000</t>
+          <t>0.94%426,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>135000</v>
+        <v>426000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+4.12%2530</t>
+          <t>+2.45%293</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2530</v>
+        <v>293</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.84%80,000</t>
+          <t>0.85%695,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>80000</v>
+        <v>695000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+10%286</t>
+          <t>0%2530</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>286</v>
+        <v>2530</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.82%695,000</t>
+          <t>0.85%80,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>695000</v>
+        <v>80000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.61%189.5</t>
+          <t>0%189.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.69%878,000</t>
+          <t>0.70%878,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.12%543</t>
+          <t>-1.1%537</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2615萬海</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.47%3155</t>
+          <t>+0.9%111.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3155</v>
+        <v>111.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.63%48,000</t>
+          <t>0.63%1,350,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>48000</v>
+        <v>1350000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2615萬海</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.21%110.5</t>
+          <t>-1.27%3115</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>110.5</v>
+        <v>3115</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.62%1,350,000</t>
+          <t>0.63%48,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1350000</v>
+        <v>48000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+9.95%1215</t>
+          <t>+3.7%1260</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+9.95%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1215</v>
+        <v>1260</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.57%113,000</t>
+          <t>0.60%113,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.38%794</t>
+          <t>-1.76%780</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>152.5</v>
+        <v>147.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.55%878,000</t>
+          <t>0.54%878,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+5.5%1055</t>
+          <t>-0.95%1045</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2451創見</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.17%289.5</t>
+          <t>-0.48%2090</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>289.5</v>
+        <v>2090</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.30%252,000</t>
+          <t>0.30%34,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>252000</v>
+        <v>34000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>2451創見</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0%1295</t>
+          <t>-3.63%279</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1295</v>
+        <v>279</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.30%55,294</t>
+          <t>0.29%252,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>55294</v>
+        <v>252000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.24%2100</t>
+          <t>-2.32%1265</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-2.32%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2100</v>
+        <v>1265</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.30%34,000</t>
+          <t>0.29%55,294</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>34000</v>
+        <v>55294</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2.15%1190</t>
+          <t>-1.26%1175</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1190</v>
+        <v>1175</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:29</t>
+          <t>2026-10-06 19:17:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.05%378</t>
+          <t>-2.12%370</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.28%176,828</t>
+          <t>0.27%176,828</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:30</t>
+          <t>2026-10-06 19:17:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.13%755</t>
+          <t>0%755</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:30</t>
+          <t>2026-10-06 19:17:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+6.35%620</t>
+          <t>-0.16%619</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+6.35%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:30</t>
+          <t>2026-10-06 19:17:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.12%181</t>
+          <t>-1.93%177.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>181</v>
+        <v>177.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:30</t>
+          <t>2026-10-06 19:17:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%1180</t>
+          <t>+1.27%1195</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1180</v>
+        <v>1195</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.06%13,000</t>
+          <t>0.07%13,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:30</t>
+          <t>2026-10-06 19:17:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.34%145.5</t>
+          <t>0%145.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:34</t>
+          <t>2026-10-06 23:20:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:35</t>
+          <t>2026-10-06 23:20:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:36</t>
+          <t>2026-10-06 23:20:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:38</t>
+          <t>2026-10-06 23:20:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:38</t>
+          <t>2026-10-06 23:20:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:38</t>
+          <t>2026-10-06 23:20:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:38</t>
+          <t>2026-10-06 23:20:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:38</t>
+          <t>2026-10-06 23:20:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:05</t>
+          <t>2026-10-06 23:28:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:06</t>
+          <t>2026-10-06 23:28:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:07</t>
+          <t>2026-10-06 23:28:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:09</t>
+          <t>2026-10-06 23:28:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:09</t>
+          <t>2026-10-06 23:28:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:09</t>
+          <t>2026-10-06 23:28:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:09</t>
+          <t>2026-10-06 23:28:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:20:09</t>
+          <t>2026-10-06 23:28:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:39</t>
+          <t>2026-10-06 23:59:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:40</t>
+          <t>2026-10-06 23:59:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:41</t>
+          <t>2026-10-06 23:59:16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:43</t>
+          <t>2026-10-06 23:59:17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
